--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260704_204509.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260704_204509.xlsx
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260704_204509.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260704_204509.xlsx
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260704_204509.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260704_204509.xlsx
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
